--- a/fl-structure-2.2.0/ig/StructureDefinition-fr-core-organization-uac.xlsx
+++ b/fl-structure-2.2.0/ig/StructureDefinition-fr-core-organization-uac.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-07T13:17:22+00:00</t>
+    <t>2026-02-07T19:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -695,10 +695,10 @@
     <t>closureReason</t>
   </si>
   <si>
-    <t>Organization.extension:members</t>
-  </si>
-  <si>
-    <t>members</t>
+    <t>Organization.extension:member</t>
+  </si>
+  <si>
+    <t>member</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}
